--- a/gte/nodes/LPC/compressor_stage_3_blade_stator_coordinates_lattice.xlsx
+++ b/gte/nodes/LPC/compressor_stage_3_blade_stator_coordinates_lattice.xlsx
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>18.426640016956672</v>
+        <v>18.502299558541882</v>
       </c>
       <c r="B2">
-        <v>20.767171458359034</v>
+        <v>20.675400821326935</v>
       </c>
       <c r="C2">
         <v>338.16769933532214</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>16.807901575403072</v>
+        <v>16.912189051642144</v>
       </c>
       <c r="B3">
-        <v>20.203958637471523</v>
+        <v>20.077463975616475</v>
       </c>
       <c r="C3">
         <v>338.16769933532214</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>15.23048395983931</v>
+        <v>15.356855842811353</v>
       </c>
       <c r="B4">
-        <v>19.590626050532979</v>
+        <v>19.4373442838145</v>
       </c>
       <c r="C4">
         <v>338.16769933532214</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>13.685236639605021</v>
+        <v>13.829398739111969</v>
       </c>
       <c r="B5">
-        <v>18.938272760666006</v>
+        <v>18.76341249280755</v>
       </c>
       <c r="C5">
         <v>338.16769933532214</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>12.168351416755805</v>
+        <v>12.326925924377616</v>
       </c>
       <c r="B6">
-        <v>18.251517891169279</v>
+        <v>18.059176207931404</v>
       </c>
       <c r="C6">
         <v>338.16769933532214</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>10.677608166901734</v>
+        <v>10.847739892844684</v>
       </c>
       <c r="B7">
-        <v>17.533054324199952</v>
+        <v>17.3266944052521</v>
       </c>
       <c r="C7">
         <v>338.16769933532214</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>9.2116561431459925</v>
+        <v>9.39079675038231</v>
       </c>
       <c r="B8">
-        <v>16.784520437424529</v>
+        <v>16.56723326782306</v>
       </c>
       <c r="C8">
         <v>338.16769933532214</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>7.7684639170420589</v>
+        <v>7.954545492292155</v>
       </c>
       <c r="B9">
-        <v>16.008380235761823</v>
+        <v>15.782674074412608</v>
       </c>
       <c r="C9">
         <v>338.16769933532214</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>6.345852916210367</v>
+        <v>6.5373263671407109</v>
       </c>
       <c r="B10">
-        <v>15.207276201189719</v>
+        <v>14.975030007273478</v>
       </c>
       <c r="C10">
         <v>338.16769933532214</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>4.94173667408877</v>
+        <v>5.1375517471211838</v>
       </c>
       <c r="B11">
-        <v>14.383739096670066</v>
+        <v>14.146226766881046</v>
       </c>
       <c r="C11">
         <v>338.16769933532214</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>3.5549661843916751</v>
+        <v>3.7543385733532828</v>
       </c>
       <c r="B12">
-        <v>13.539162600205312</v>
+        <v>13.297335452455375</v>
       </c>
       <c r="C12">
         <v>338.16769933532214</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>2.18805017612225</v>
+        <v>2.3895499390359283</v>
       </c>
       <c r="B13">
-        <v>12.67050376897638</v>
+        <v>12.426096239972518</v>
       </c>
       <c r="C13">
         <v>338.16769933532214</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>0.84246610833034219</v>
+        <v>1.0442769313497529</v>
       </c>
       <c r="B14">
-        <v>11.775970530822216</v>
+        <v>11.531185703946068</v>
       </c>
       <c r="C14">
         <v>338.16769933532214</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-0.48809137503629496</v>
+        <v>-0.28622353867706685</v>
       </c>
       <c r="B15">
-        <v>10.863210917035426</v>
+        <v>10.618356936283842</v>
       </c>
       <c r="C15">
         <v>338.16769933532214</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.8094052718996097</v>
+        <v>-1.606301564959246</v>
       </c>
       <c r="B16">
-        <v>9.9392393687840883</v>
+        <v>9.692886348676149</v>
       </c>
       <c r="C16">
         <v>338.16769933532214</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.117386332558322</v>
+        <v>-2.9129010850307395</v>
       </c>
       <c r="B17">
-        <v>8.99909586328446</v>
+        <v>8.75106711454906</v>
       </c>
       <c r="C17">
         <v>338.16769933532214</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-4.4067357354432657</v>
+        <v>-4.202057300532644</v>
       </c>
       <c r="B18">
-        <v>8.0363532372107631</v>
+        <v>7.7880901633811757</v>
       </c>
       <c r="C18">
         <v>338.16769933532214</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-5.677188619136964</v>
+        <v>-5.4735766259154008</v>
       </c>
       <c r="B19">
-        <v>7.05069022902087</v>
+        <v>6.8037206871254172</v>
       </c>
       <c r="C19">
         <v>338.16769933532214</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-6.9297386122598787</v>
+        <v>-6.7282082788318114</v>
       </c>
       <c r="B20">
-        <v>6.0433120526185524</v>
+        <v>5.7988674433532834</v>
       </c>
       <c r="C20">
         <v>338.16769933532214</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-8.1653793434324484</v>
+        <v>-7.96670147693465</v>
       </c>
       <c r="B21">
-        <v>5.0154239219075913</v>
+        <v>4.7744391896362792</v>
       </c>
       <c r="C21">
         <v>338.16769933532214</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-9.3849252513759058</v>
+        <v>-9.1896697394284033</v>
       </c>
       <c r="B22">
-        <v>3.9680137038338454</v>
+        <v>3.7311800891962115</v>
       </c>
       <c r="C22">
         <v>338.16769933532214</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-10.588474015214587</v>
+        <v>-10.39718379172434</v>
       </c>
       <c r="B23">
-        <v>2.9011998775114707</v>
+        <v>2.6691759278561227</v>
       </c>
       <c r="C23">
         <v>338.16769933532214</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-11.775944124173602</v>
+        <v>-11.589178660785404</v>
       </c>
       <c r="B24">
-        <v>1.8148835750967183</v>
+        <v>1.5883478970893694</v>
       </c>
       <c r="C24">
         <v>338.16769933532214</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-12.94725406747807</v>
+        <v>-12.765589373574567</v>
       </c>
       <c r="B25">
-        <v>0.70896592874582043</v>
+        <v>0.48861718836929174</v>
       </c>
       <c r="C25">
         <v>338.16769933532214</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-14.102288628970593</v>
+        <v>-13.926324395876987</v>
       </c>
       <c r="B26">
-        <v>-0.41669281205962588</v>
+        <v>-0.6301272239993142</v>
       </c>
       <c r="C26">
         <v>338.16769933532214</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-15.240797770963789</v>
+        <v>-15.071185948766729</v>
       </c>
       <c r="B27">
-        <v>-1.5623959285366948</v>
+        <v>-1.7681252343859739</v>
       </c>
       <c r="C27">
         <v>338.16769933532214</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-16.362497750387767</v>
+        <v>-16.199949692140066</v>
       </c>
       <c r="B28">
-        <v>-2.7284875845771053</v>
+        <v>-2.9256489543287674</v>
       </c>
       <c r="C28">
         <v>338.16769933532214</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-17.467104824172623</v>
+        <v>-17.312391285893252</v>
       </c>
       <c r="B29">
-        <v>-3.9153119440725619</v>
+        <v>-4.1029704953657662</v>
       </c>
       <c r="C29">
         <v>338.16769933532214</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-18.554459574139813</v>
+        <v>-18.40837826556082</v>
       </c>
       <c r="B30">
-        <v>-5.1230623720302395</v>
+        <v>-5.3002505292130193</v>
       </c>
       <c r="C30">
         <v>338.16769933532214</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-19.624899881676107</v>
+        <v>-19.488145669230267</v>
       </c>
       <c r="B31">
-        <v>-6.3513290379190694</v>
+        <v>-6.5172039682983982</v>
       </c>
       <c r="C31">
         <v>338.16769933532214</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-20.678887953059665</v>
+        <v>-20.552020410627364</v>
       </c>
       <c r="B32">
-        <v>-7.5995513123234515</v>
+        <v>-7.7534342852277627</v>
       </c>
       <c r="C32">
         <v>338.16769933532214</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-21.716885994568607</v>
+        <v>-21.600329403477886</v>
       </c>
       <c r="B33">
-        <v>-8.8671685658277788</v>
+        <v>-9.0085449526069556</v>
       </c>
       <c r="C33">
         <v>338.16769933532214</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-22.73914045700613</v>
+        <v>-22.633236167036443</v>
       </c>
       <c r="B34">
-        <v>-10.153881867897528</v>
+        <v>-10.282337631061317</v>
       </c>
       <c r="C34">
         <v>338.16769933532214</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-23.745034769275733</v>
+        <v>-23.650250642673157</v>
       </c>
       <c r="B35">
-        <v>-11.460439083522589</v>
+        <v>-11.57540673329421</v>
       </c>
       <c r="C35">
         <v>338.16769933532214</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-24.733736604805973</v>
+        <v>-24.650719377286986</v>
       </c>
       <c r="B36">
-        <v>-12.787849776573928</v>
+        <v>-12.888544860028487</v>
       </c>
       <c r="C36">
         <v>338.16769933532214</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-25.704413637025421</v>
+        <v>-25.633988917776922</v>
       </c>
       <c r="B37">
-        <v>-14.137123510922544</v>
+        <v>-14.222544611987013</v>
       </c>
       <c r="C37">
         <v>338.16769933532214</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-26.655713323035506</v>
+        <v>-26.59901404979119</v>
       </c>
       <c r="B38">
-        <v>-15.509900842680921</v>
+        <v>-15.578673773574609</v>
       </c>
       <c r="C38">
         <v>338.16769933532214</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-27.584202254629044</v>
+        <v>-27.543182513975012</v>
       </c>
       <c r="B39">
-        <v>-16.910346296927589</v>
+        <v>-16.960100863923909</v>
       </c>
       <c r="C39">
         <v>338.16769933532214</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-28.485926807271756</v>
+        <v>-28.463490289722895</v>
       </c>
       <c r="B40">
-        <v>-18.343255390982616</v>
+        <v>-18.370469585849527</v>
       </c>
       <c r="C40">
         <v>338.16769933532214</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-28.306434666880882</v>
+        <v>-28.32887118442974</v>
       </c>
       <c r="B43">
-        <v>-18.560968949917882</v>
+        <v>-18.533754755050971</v>
       </c>
       <c r="C43">
         <v>338.16769933532214</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-27.256044329396786</v>
+        <v>-27.297064070050819</v>
       </c>
       <c r="B44">
-        <v>-17.308382832898161</v>
+        <v>-17.258628265901841</v>
       </c>
       <c r="C44">
         <v>338.16769933532214</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-26.202119137080995</v>
+        <v>-26.258818410325304</v>
       </c>
       <c r="B45">
-        <v>-16.060084289830456</v>
+        <v>-15.991311358936763</v>
       </c>
       <c r="C45">
         <v>338.16769933532214</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-25.141015883037436</v>
+        <v>-25.211440602285933</v>
       </c>
       <c r="B46">
-        <v>-14.820492319438323</v>
+        <v>-14.735071218373845</v>
       </c>
       <c r="C46">
         <v>338.16769933532214</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-24.069598784654112</v>
+        <v>-24.152616012173088</v>
       </c>
       <c r="B47">
-        <v>-13.59341044421039</v>
+        <v>-13.492715360755833</v>
       </c>
       <c r="C47">
         <v>338.16769933532214</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-22.986761756455135</v>
+        <v>-23.081545883057707</v>
       </c>
       <c r="B48">
-        <v>-12.380180281695578</v>
+        <v>-12.265212631923951</v>
       </c>
       <c r="C48">
         <v>338.16769933532214</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-21.891906137248657</v>
+        <v>-21.99781042721834</v>
       </c>
       <c r="B49">
-        <v>-11.181527973207855</v>
+        <v>-11.053072210044062</v>
       </c>
       <c r="C49">
         <v>338.16769933532214</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-20.78443326584285</v>
+        <v>-20.900989856933563</v>
       </c>
       <c r="B50">
-        <v>-9.9981796600612078</v>
+        <v>-9.8568032732820274</v>
       </c>
       <c r="C50">
         <v>338.16769933532214</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-19.663947613601291</v>
+        <v>-19.790815156033585</v>
       </c>
       <c r="B51">
-        <v>-8.8306150955579472</v>
+        <v>-8.6767321226536342</v>
       </c>
       <c r="C51">
         <v>338.16769933532214</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-18.530866182109378</v>
+        <v>-18.667620394555215</v>
       </c>
       <c r="B52">
-        <v>-7.6783284809537182</v>
+        <v>-7.5124535505743832</v>
       </c>
       <c r="C52">
         <v>338.16769933532214</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-17.38580910550791</v>
+        <v>-17.531890414086895</v>
       </c>
       <c r="B53">
-        <v>-6.5405676294924833</v>
+        <v>-6.3633794723097017</v>
       </c>
       <c r="C53">
         <v>338.16769933532214</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-16.229396517937694</v>
+        <v>-16.384110056217057</v>
       </c>
       <c r="B54">
-        <v>-5.4165803544181994</v>
+        <v>-5.2289218031249938</v>
       </c>
       <c r="C54">
         <v>338.16769933532214</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-15.062113284406188</v>
+        <v>-15.224661342653882</v>
       </c>
       <c r="B55">
-        <v>-4.3057785425904171</v>
+        <v>-4.10861717283875</v>
       </c>
       <c r="C55">
         <v>338.16769933532214</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-13.883903193387347</v>
+        <v>-14.053515015584399</v>
       </c>
       <c r="B56">
-        <v>-3.2082303753309351</v>
+        <v>-3.0025010694816525</v>
       </c>
       <c r="C56">
         <v>338.16769933532214</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-12.694574764221775</v>
+        <v>-12.870538997315373</v>
       </c>
       <c r="B57">
-        <v>-2.1241681075771441</v>
+        <v>-1.9107336956374534</v>
       </c>
       <c r="C57">
         <v>338.16769933532214</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-11.493936516250063</v>
+        <v>-11.675601210153562</v>
       </c>
       <c r="B58">
-        <v>-1.053823994266424</v>
+        <v>-0.833475253889892</v>
       </c>
       <c r="C58">
         <v>338.16769933532214</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-10.281820417068051</v>
+        <v>-10.468585880456242</v>
       </c>
       <c r="B59">
-        <v>0.0025981510379047626</v>
+        <v>0.22913382904525895</v>
       </c>
       <c r="C59">
         <v>338.16769933532214</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-9.0581522272926271</v>
+        <v>-9.249442450782869</v>
       </c>
       <c r="B60">
-        <v>1.0450082802686687</v>
+        <v>1.2770322299240209</v>
       </c>
       <c r="C60">
         <v>338.16769933532214</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-7.8228811557959235</v>
+        <v>-8.018136667743418</v>
       </c>
       <c r="B61">
-        <v>2.0733447867327635</v>
+        <v>2.3101784013704005</v>
       </c>
       <c r="C61">
         <v>338.16769933532214</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-6.5759564114500835</v>
+        <v>-6.7746342779478761</v>
       </c>
       <c r="B62">
-        <v>3.0875460637370633</v>
+        <v>3.3285307960083816</v>
       </c>
       <c r="C62">
         <v>338.16769933532214</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-5.3174959448353585</v>
+        <v>-5.5190262782634205</v>
       </c>
       <c r="B63">
-        <v>4.0877551784963844</v>
+        <v>4.3321997877616569</v>
       </c>
       <c r="C63">
         <v>338.16769933532214</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-4.04829267336448</v>
+        <v>-4.2519046665860376</v>
       </c>
       <c r="B64">
-        <v>5.074933893857235</v>
+        <v>5.3219034357526915</v>
       </c>
       <c r="C64">
         <v>338.16769933532214</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.7693082561583093</v>
+        <v>-2.9739866910689261</v>
       </c>
       <c r="B65">
-        <v>6.050248646574043</v>
+        <v>6.2985117204036358</v>
       </c>
       <c r="C65">
         <v>338.16769933532214</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-1.481504352337691</v>
+        <v>-1.685989599865267</v>
       </c>
       <c r="B66">
-        <v>7.0148658734012486</v>
+        <v>7.2628946221366517</v>
       </c>
       <c r="C66">
         <v>338.16769933532214</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-0.18457561637672676</v>
+        <v>-0.38767932331708421</v>
       </c>
       <c r="B67">
-        <v>7.9684152079205486</v>
+        <v>8.2147682280284933</v>
       </c>
       <c r="C67">
         <v>338.16769933532214</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>1.1268513158375098</v>
+        <v>0.92498347947828685</v>
       </c>
       <c r="B68">
-        <v>8.9043790710227224</v>
+        <v>9.1492330517743117</v>
       </c>
       <c r="C68">
         <v>338.16769933532214</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>2.456952692485598</v>
+        <v>2.2551418694661929</v>
       </c>
       <c r="B69">
-        <v>9.8176919158130165</v>
+        <v>10.062476742689169</v>
       </c>
       <c r="C69">
         <v>338.16769933532214</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>3.8000482794316581</v>
+        <v>3.5985485165179845</v>
       </c>
       <c r="B70">
-        <v>10.715243536945463</v>
+        <v>10.959651065949331</v>
       </c>
       <c r="C70">
         <v>338.16769933532214</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5.1499452960845025</v>
+        <v>4.9505729071229032</v>
       </c>
       <c r="B71">
-        <v>11.604545418205815</v>
+        <v>11.846372565955756</v>
       </c>
       <c r="C71">
         <v>338.16769933532214</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6.5082572583480456</v>
+        <v>6.3124421853156409</v>
       </c>
       <c r="B72">
-        <v>12.4836404583579</v>
+        <v>12.721152788146926</v>
       </c>
       <c r="C72">
         <v>338.16769933532214</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>7.8776405236530911</v>
+        <v>7.6861670727227542</v>
       </c>
       <c r="B73">
-        <v>13.34930664985975</v>
+        <v>13.581552843775999</v>
       </c>
       <c r="C73">
         <v>338.16769933532214</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>9.2571165190428317</v>
+        <v>9.0710349437927373</v>
       </c>
       <c r="B74">
-        <v>14.202730944968101</v>
+        <v>14.428437106317317</v>
       </c>
       <c r="C74">
         <v>338.16769933532214</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>10.644781001036529</v>
+        <v>10.465640393800214</v>
       </c>
       <c r="B75">
-        <v>15.046223080612762</v>
+        <v>15.263510250214234</v>
       </c>
       <c r="C75">
         <v>338.16769933532214</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>12.038661974445297</v>
+        <v>11.868530248502356</v>
       </c>
       <c r="B76">
-        <v>15.882174972617122</v>
+        <v>16.088534891564976</v>
       </c>
       <c r="C76">
         <v>338.16769933532214</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>13.436947477730252</v>
+        <v>13.278372970108448</v>
       </c>
       <c r="B77">
-        <v>16.712784425266246</v>
+        <v>16.905126108504128</v>
       </c>
       <c r="C77">
         <v>338.16769933532214</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>14.838533435660565</v>
+        <v>14.694371336153626</v>
       </c>
       <c r="B78">
-        <v>17.53939061779834</v>
+        <v>17.7142508856568</v>
       </c>
       <c r="C78">
         <v>338.16769933532214</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>16.241459023615658</v>
+        <v>16.115087140643617</v>
       </c>
       <c r="B79">
-        <v>18.364371916785156</v>
+        <v>18.517653683503635</v>
       </c>
       <c r="C79">
         <v>338.16769933532214</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>17.642201385315595</v>
+        <v>17.537913909076536</v>
       </c>
       <c r="B80">
-        <v>19.192001342631087</v>
+        <v>19.318496004486146</v>
       </c>
       <c r="C80">
         <v>338.16769933532214</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>19.031916349638308</v>
+        <v>18.956256808053109</v>
       </c>
       <c r="B81">
-        <v>20.033006362102242</v>
+        <v>20.12477699913434</v>
       </c>
       <c r="C81">
         <v>338.16769933532214</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>17.936207796742682</v>
+        <v>18.028629265068805</v>
       </c>
       <c r="B2">
-        <v>25.110057174253509</v>
+        <v>25.016087328615512</v>
       </c>
       <c r="C2">
         <v>410.1621514722421</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>16.111097256273112</v>
+        <v>16.238489009911827</v>
       </c>
       <c r="B3">
-        <v>24.425668483449773</v>
+        <v>24.296142480002803</v>
       </c>
       <c r="C3">
         <v>410.1621514722421</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>14.353924393833786</v>
+        <v>14.50829322471364</v>
       </c>
       <c r="B4">
-        <v>23.672203924959337</v>
+        <v>23.515248885488308</v>
       </c>
       <c r="C4">
         <v>410.1621514722421</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>12.64797195464587</v>
+        <v>12.824072319969975</v>
       </c>
       <c r="B5">
-        <v>22.866660825047518</v>
+        <v>22.687610173223767</v>
       </c>
       <c r="C5">
         <v>410.1621514722421</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>10.986308626669649</v>
+        <v>11.180014384415951</v>
       </c>
       <c r="B6">
-        <v>22.016086619058466</v>
+        <v>21.819135623967366</v>
       </c>
       <c r="C6">
         <v>410.1621514722421</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>9.36490922794191</v>
+        <v>9.5727326377995769</v>
       </c>
       <c r="B7">
-        <v>21.124573924590656</v>
+        <v>20.913268758183051</v>
       </c>
       <c r="C7">
         <v>410.1621514722421</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>7.7813396938066219</v>
+        <v>8.000167849657517</v>
       </c>
       <c r="B8">
-        <v>20.194597585250698</v>
+        <v>19.972103305523451</v>
       </c>
       <c r="C8">
         <v>410.1621514722421</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>6.2319146573602433</v>
+        <v>6.4592215118920659</v>
       </c>
       <c r="B9">
-        <v>19.229904710506943</v>
+        <v>18.99878968474863</v>
       </c>
       <c r="C9">
         <v>410.1621514722421</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>4.7126771593168453</v>
+        <v>4.9465704278945282</v>
       </c>
       <c r="B10">
-        <v>18.234518552316224</v>
+        <v>17.996706767434659</v>
       </c>
       <c r="C10">
         <v>410.1621514722421</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>3.2198351731083088</v>
+        <v>3.4590319246464127</v>
       </c>
       <c r="B11">
-        <v>17.212294666727527</v>
+        <v>16.969090547314163</v>
       </c>
       <c r="C11">
         <v>410.1621514722421</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>1.7513125098854261</v>
+        <v>1.994854679788322</v>
       </c>
       <c r="B12">
-        <v>16.16534402589059</v>
+        <v>15.91772168741657</v>
       </c>
       <c r="C12">
         <v>410.1621514722421</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>0.31173139895674612</v>
+        <v>0.55787225000692064</v>
       </c>
       <c r="B13">
-        <v>15.08896696226611</v>
+        <v>14.838702405802106</v>
       </c>
       <c r="C13">
         <v>410.1621514722421</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.0961774582051302</v>
+        <v>-0.84965663351108978</v>
       </c>
       <c r="B14">
-        <v>13.980387025744486</v>
+        <v>13.729736129771846</v>
       </c>
       <c r="C14">
         <v>410.1621514722421</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.4839478896291554</v>
+        <v>-2.2373574206249609</v>
       </c>
       <c r="B15">
-        <v>12.851331275624006</v>
+        <v>12.600609568559602</v>
       </c>
       <c r="C15">
         <v>410.1621514722421</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.8621582563692831</v>
+        <v>-3.6140581169206687</v>
       </c>
       <c r="B16">
-        <v>11.712555296871527</v>
+        <v>11.460298627192962</v>
       </c>
       <c r="C16">
         <v>410.1621514722421</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-5.2233005220779374</v>
+        <v>-4.973512769845164</v>
       </c>
       <c r="B17">
-        <v>10.556425267720258</v>
+        <v>10.302452711941889</v>
       </c>
       <c r="C17">
         <v>410.1621514722421</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-6.5576524914968477</v>
+        <v>-6.3076287523518015</v>
       </c>
       <c r="B18">
-        <v>9.3730561127193575</v>
+        <v>9.1188436164366831</v>
       </c>
       <c r="C18">
         <v>410.1621514722421</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-7.8647217311265223</v>
+        <v>-7.6160006975586176</v>
       </c>
       <c r="B19">
-        <v>8.1619471484153756</v>
+        <v>7.9090591825065717</v>
       </c>
       <c r="C19">
         <v>410.1621514722421</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-9.14632324790717</v>
+        <v>-8.9001450536248257</v>
       </c>
       <c r="B20">
-        <v>6.9249437893542156</v>
+        <v>6.6746412640305257</v>
       </c>
       <c r="C20">
         <v>410.1621514722421</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-10.404272048778985</v>
+        <v>-10.161578268709624</v>
       </c>
       <c r="B21">
-        <v>5.6638914500817839</v>
+        <v>5.4171317148875238</v>
       </c>
       <c r="C21">
         <v>410.1621514722421</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-11.640056650718677</v>
+        <v>-11.401543427734966</v>
       </c>
       <c r="B22">
-        <v>4.3803035853512116</v>
+        <v>4.1377944459452918</v>
       </c>
       <c r="C22">
         <v>410.1621514722421</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-12.853859610848909</v>
+        <v>-12.620190162673737</v>
       </c>
       <c r="B23">
-        <v>3.0743658107445513</v>
+        <v>2.8367815960266629</v>
       </c>
       <c r="C23">
         <v>410.1621514722421</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-14.045536996328842</v>
+        <v>-13.817394742261552</v>
       </c>
       <c r="B24">
-        <v>1.7459317820510871</v>
+        <v>1.5139673609432351</v>
       </c>
       <c r="C24">
         <v>410.1621514722421</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-15.214944874317643</v>
+        <v>-14.993033435234047</v>
       </c>
       <c r="B25">
-        <v>0.39485515506009272</v>
+        <v>0.16922593650659043</v>
       </c>
       <c r="C25">
         <v>410.1621514722421</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-16.361879339826078</v>
+        <v>-16.146931265139731</v>
       </c>
       <c r="B26">
-        <v>-0.979071391327184</v>
+        <v>-1.1976205851918176</v>
       </c>
       <c r="C26">
         <v>410.1621514722421</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-17.485896599271356</v>
+        <v>-17.27870827477869</v>
       </c>
       <c r="B27">
-        <v>-2.3762990857617</v>
+        <v>-2.5869585269412045</v>
       </c>
       <c r="C27">
         <v>410.1621514722421</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-18.586492886922276</v>
+        <v>-18.387933261763898</v>
       </c>
       <c r="B28">
-        <v>-3.7973401337824346</v>
+        <v>-3.9992263152509087</v>
       </c>
       <c r="C28">
         <v>410.1621514722421</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-19.663164437047641</v>
+        <v>-19.474175023708323</v>
       </c>
       <c r="B29">
-        <v>-5.2427067409283694</v>
+        <v>-5.4348623766302833</v>
       </c>
       <c r="C29">
         <v>410.1621514722421</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-20.715637125694695</v>
+        <v>-20.537192361808994</v>
       </c>
       <c r="B30">
-        <v>-6.7126776236708441</v>
+        <v>-6.8941119507914372</v>
       </c>
       <c r="C30">
         <v>410.1621514722421</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-21.744555396024385</v>
+        <v>-21.577504091599096</v>
       </c>
       <c r="B31">
-        <v>-8.206597542210547</v>
+        <v>-8.3764475302574546</v>
       </c>
       <c r="C31">
         <v>410.1621514722421</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-22.750793332976098</v>
+        <v>-22.595819032195866</v>
       </c>
       <c r="B32">
-        <v>-9.7235777676805331</v>
+        <v>-9.8811484207541973</v>
       </c>
       <c r="C32">
         <v>410.1621514722421</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-23.735225021489207</v>
+        <v>-23.592846002716531</v>
       </c>
       <c r="B33">
-        <v>-11.262729571213832</v>
+        <v>-11.407493928007503</v>
       </c>
       <c r="C33">
         <v>410.1621514722421</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-24.698331190240896</v>
+        <v>-24.568964427292546</v>
       </c>
       <c r="B34">
-        <v>-12.82356417027532</v>
+        <v>-12.955098271227355</v>
       </c>
       <c r="C34">
         <v>410.1621514722421</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-25.639019142859546</v>
+        <v>-25.523236150112304</v>
       </c>
       <c r="B35">
-        <v>-14.407192567657218</v>
+        <v>-14.524915323560327</v>
       </c>
       <c r="C35">
         <v>410.1621514722421</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-26.555802826711314</v>
+        <v>-26.45439362037839</v>
       </c>
       <c r="B36">
-        <v>-16.01512571248357</v>
+        <v>-16.118233871637138</v>
       </c>
       <c r="C36">
         <v>410.1621514722421</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-27.44719618916238</v>
+        <v>-27.361169287293414</v>
       </c>
       <c r="B37">
-        <v>-17.648874553878436</v>
+        <v>-17.736342702088503</v>
       </c>
       <c r="C37">
         <v>410.1621514722421</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-28.310761810236585</v>
+        <v>-28.241501146261214</v>
       </c>
       <c r="B38">
-        <v>-19.310917346981689</v>
+        <v>-19.381338365176131</v>
       </c>
       <c r="C38">
         <v>410.1621514722421</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-29.140256800588435</v>
+        <v>-29.09014937749054</v>
       </c>
       <c r="B39">
-        <v>-21.007601570996552</v>
+        <v>-21.058548465685696</v>
       </c>
       <c r="C39">
         <v>410.1621514722421</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-29.928486903530107</v>
+        <v>-29.9010797073914</v>
       </c>
       <c r="B40">
-        <v>-22.746242011142073</v>
+        <v>-22.774108372033862</v>
       </c>
       <c r="C40">
         <v>410.1621514722421</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-29.599600549865606</v>
+        <v>-29.627007746004313</v>
       </c>
       <c r="B43">
-        <v>-23.080638341843521</v>
+        <v>-23.052771980951736</v>
       </c>
       <c r="C43">
         <v>410.1621514722421</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-28.538967723413702</v>
+        <v>-28.589075146511597</v>
       </c>
       <c r="B44">
-        <v>-21.618964307266246</v>
+        <v>-21.568017412577102</v>
       </c>
       <c r="C44">
         <v>410.1621514722421</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-27.479633842532088</v>
+        <v>-27.548894506507466</v>
       </c>
       <c r="B45">
-        <v>-20.155969565314987</v>
+        <v>-20.085548547120545</v>
       </c>
       <c r="C45">
         <v>410.1621514722421</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-26.414873366734774</v>
+        <v>-26.50090026860374</v>
       </c>
       <c r="B46">
-        <v>-18.69849233239928</v>
+        <v>-18.611024184189208</v>
       </c>
       <c r="C46">
         <v>410.1621514722421</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-25.338892350716215</v>
+        <v>-25.440301557049139</v>
       </c>
       <c r="B47">
-        <v>-17.25242362232639</v>
+        <v>-17.149315463172822</v>
       </c>
       <c r="C47">
         <v>410.1621514722421</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-24.249623229892631</v>
+        <v>-24.365406222639876</v>
       </c>
       <c r="B48">
-        <v>-15.819865638494552</v>
+        <v>-15.702142882591437</v>
       </c>
       <c r="C48">
         <v>410.1621514722421</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-23.145930034860683</v>
+        <v>-23.275296797809034</v>
       </c>
       <c r="B49">
-        <v>-14.401973381699722</v>
+        <v>-14.270439280747688</v>
       </c>
       <c r="C49">
         <v>410.1621514722421</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-22.026676796217036</v>
+        <v>-22.169055814989715</v>
       </c>
       <c r="B50">
-        <v>-12.999901852737878</v>
+        <v>-12.855137495944208</v>
       </c>
       <c r="C50">
         <v>410.1621514722421</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-20.8911017236133</v>
+        <v>-21.046076024393532</v>
       </c>
       <c r="B51">
-        <v>-11.614425604564536</v>
+        <v>-11.45685495149087</v>
       </c>
       <c r="C51">
         <v>410.1621514722421</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-19.739939742920921</v>
+        <v>-19.90699104734621</v>
       </c>
       <c r="B52">
-        <v>-10.244797398773459</v>
+        <v>-10.074947410726548</v>
       </c>
       <c r="C52">
         <v>410.1621514722421</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-18.574299959066302</v>
+        <v>-18.752744722952002</v>
       </c>
       <c r="B53">
-        <v>-8.8898895491179566</v>
+        <v>-8.7084552219973652</v>
       </c>
       <c r="C53">
         <v>410.1621514722421</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-17.395291476975839</v>
+        <v>-17.584280890315156</v>
       </c>
       <c r="B54">
-        <v>-7.5485743693513383</v>
+        <v>-7.3564187336494244</v>
       </c>
       <c r="C54">
         <v>410.1621514722421</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-16.203777385021731</v>
+        <v>-16.402337010180108</v>
       </c>
       <c r="B55">
-        <v>-6.2199743114041395</v>
+        <v>-6.0180881299356637</v>
       </c>
       <c r="C55">
         <v>410.1621514722421</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-14.99963670535935</v>
+        <v>-15.206825029852018</v>
       </c>
       <c r="B56">
-        <v>-4.9042123799157551</v>
+        <v>-4.6935529387362491</v>
       </c>
       <c r="C56">
         <v>410.1621514722421</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-13.782502443589875</v>
+        <v>-13.997450518276226</v>
       </c>
       <c r="B57">
-        <v>-3.6016617177028136</v>
+        <v>-3.3831125238381774</v>
       </c>
       <c r="C57">
         <v>410.1621514722421</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-12.552007605314486</v>
+        <v>-12.773919044398081</v>
       </c>
       <c r="B58">
-        <v>-2.3126954675819444</v>
+        <v>-2.0870662490284415</v>
       </c>
       <c r="C58">
         <v>410.1621514722421</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-11.307829947521368</v>
+        <v>-11.535972201588658</v>
       </c>
       <c r="B59">
-        <v>-1.0376412712431631</v>
+        <v>-0.80567685013530843</v>
       </c>
       <c r="C59">
         <v>410.1621514722421</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-10.049826232746817</v>
+        <v>-10.283495680921991</v>
       </c>
       <c r="B60">
-        <v>0.22335523412988276</v>
+        <v>0.46093944884777194</v>
       </c>
       <c r="C60">
         <v>410.1621514722421</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-8.77789797491413</v>
+        <v>-9.0164111978978436</v>
       </c>
       <c r="B61">
-        <v>1.4701939124801606</v>
+        <v>1.7127030518860817</v>
       </c>
       <c r="C61">
         <v>410.1621514722421</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-7.4919466879466263</v>
+        <v>-7.73464046801599</v>
       </c>
       <c r="B62">
-        <v>2.7027746277506228</v>
+        <v>2.9495343629448869</v>
       </c>
       <c r="C62">
         <v>410.1621514722421</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-6.1921849165190208</v>
+        <v>-6.438363110801367</v>
       </c>
       <c r="B63">
-        <v>3.9213134854699483</v>
+        <v>4.1716160107936373</v>
       </c>
       <c r="C63">
         <v>410.1621514722421</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-4.8800693283116532</v>
+        <v>-5.1287903618795587</v>
       </c>
       <c r="B64">
-        <v>5.127291557509726</v>
+        <v>5.38017952341853</v>
       </c>
       <c r="C64">
         <v>410.1621514722421</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-3.5573676217562782</v>
+        <v>-3.8073913609013266</v>
       </c>
       <c r="B65">
-        <v>6.32250615732725</v>
+        <v>6.5767186536099258</v>
       </c>
       <c r="C65">
         <v>410.1621514722421</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.2258474952846488</v>
+        <v>-2.4756352475174226</v>
       </c>
       <c r="B66">
-        <v>7.5087545983798281</v>
+        <v>7.7627271541581973</v>
       </c>
       <c r="C66">
         <v>410.1621514722421</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-0.88495658298591184</v>
+        <v>-1.1330567224345269</v>
       </c>
       <c r="B67">
-        <v>8.6854752607287349</v>
+        <v>8.9377319304073026</v>
       </c>
       <c r="C67">
         <v>410.1621514722421</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>0.47513773842118057</v>
+        <v>0.22854726941698605</v>
       </c>
       <c r="B68">
-        <v>9.8426707908511322</v>
+        <v>10.093392497915538</v>
       </c>
       <c r="C68">
         <v>410.1621514722421</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1.8620724381233633</v>
+        <v>1.615551613429322</v>
       </c>
       <c r="B69">
-        <v>10.97257627407279</v>
+        <v>11.223227170045432</v>
       </c>
       <c r="C69">
         <v>410.1621514722421</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>3.2654216115588532</v>
+        <v>3.0192807605086771</v>
       </c>
       <c r="B70">
-        <v>12.085792284698051</v>
+        <v>12.336056841162055</v>
       </c>
       <c r="C70">
         <v>410.1621514722421</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>4.6738185487201758</v>
+        <v>4.43027637881728</v>
       </c>
       <c r="B71">
-        <v>13.193875964202368</v>
+        <v>13.441498302676385</v>
       </c>
       <c r="C71">
         <v>410.1621514722421</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6.090196191565564</v>
+        <v>5.8509994400274588</v>
       </c>
       <c r="B72">
-        <v>14.293845233767129</v>
+        <v>14.537049353180494</v>
       </c>
       <c r="C72">
         <v>410.1621514722421</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>7.5193963822490506</v>
+        <v>7.2855031136713659</v>
       </c>
       <c r="B73">
-        <v>15.380777133737412</v>
+        <v>15.618588918618979</v>
       </c>
       <c r="C73">
         <v>410.1621514722421</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>8.9595969117421372</v>
+        <v>8.7322900572103137</v>
       </c>
       <c r="B74">
-        <v>16.456524401407155</v>
+        <v>16.687639427165472</v>
       </c>
       <c r="C74">
         <v>410.1621514722421</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>10.407277564017365</v>
+        <v>10.188449408166468</v>
       </c>
       <c r="B75">
-        <v>17.524666228523728</v>
+        <v>17.747160508250978</v>
       </c>
       <c r="C75">
         <v>410.1621514722421</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>11.858790146233927</v>
+        <v>11.650966736376258</v>
       </c>
       <c r="B76">
-        <v>18.588911927699414</v>
+        <v>18.800217094107019</v>
       </c>
       <c r="C76">
         <v>410.1621514722421</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>13.310777719625273</v>
+        <v>13.117071961878972</v>
       </c>
       <c r="B77">
-        <v>19.652674677965265</v>
+        <v>19.849625673056366</v>
       </c>
       <c r="C77">
         <v>410.1621514722421</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>14.761176338535138</v>
+        <v>14.585075973211032</v>
       </c>
       <c r="B78">
-        <v>20.718053003162513</v>
+        <v>20.897103654986264</v>
       </c>
       <c r="C78">
         <v>410.1621514722421</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>16.206350364392037</v>
+        <v>16.051981533512187</v>
       </c>
       <c r="B79">
-        <v>21.788743451306953</v>
+        <v>21.945698490777986</v>
       </c>
       <c r="C79">
         <v>410.1621514722421</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>17.639798299937691</v>
+        <v>17.512406546298976</v>
       </c>
       <c r="B80">
-        <v>22.871356442086153</v>
+        <v>23.000882445533122</v>
       </c>
       <c r="C80">
         <v>410.1621514722421</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>19.045265416656196</v>
+        <v>18.95284394833007</v>
       </c>
       <c r="B81">
-        <v>23.982419026597547</v>
+        <v>24.076388872235547</v>
       </c>
       <c r="C81">
         <v>410.1621514722421</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>17.431921952380367</v>
+        <v>17.538000233946612</v>
       </c>
       <c r="B2">
-        <v>28.593172865159882</v>
+        <v>28.497684911480139</v>
       </c>
       <c r="C2">
         <v>471.28397822006644</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>15.413945632491945</v>
+        <v>15.560161642218388</v>
       </c>
       <c r="B3">
-        <v>27.814641320049944</v>
+        <v>27.683022789302196</v>
       </c>
       <c r="C3">
         <v>471.28397822006644</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>13.492952881016763</v>
+        <v>13.670132281038219</v>
       </c>
       <c r="B4">
-        <v>26.948808563498755</v>
+        <v>26.78931787329854</v>
       </c>
       <c r="C4">
         <v>471.28397822006644</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>11.643427422586841</v>
+        <v>11.845549553679277</v>
       </c>
       <c r="B5">
-        <v>26.018643452886376</v>
+        <v>25.8367001897939</v>
       </c>
       <c r="C5">
         <v>471.28397822006644</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>9.85482445312826</v>
+        <v>10.077153466974991</v>
       </c>
       <c r="B6">
-        <v>25.033638051508955</v>
+        <v>24.833505260306058</v>
       </c>
       <c r="C6">
         <v>471.28397822006644</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>8.121040976407933</v>
+        <v>8.3595737609028333</v>
       </c>
       <c r="B7">
-        <v>23.999286062818371</v>
+        <v>23.784567204814202</v>
       </c>
       <c r="C7">
         <v>471.28397822006644</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>6.4384062427651676</v>
+        <v>6.6895699079978153</v>
       </c>
       <c r="B8">
-        <v>22.918891767091395</v>
+        <v>22.692803032643038</v>
       </c>
       <c r="C8">
         <v>471.28397822006644</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>4.8013286705233078</v>
+        <v>5.0622239035646066</v>
       </c>
       <c r="B9">
-        <v>21.797488510308479</v>
+        <v>21.562639759366419</v>
       </c>
       <c r="C9">
         <v>471.28397822006644</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>3.2037982428052296</v>
+        <v>3.4722531424080176</v>
       </c>
       <c r="B10">
-        <v>20.640486299161907</v>
+        <v>20.398832601158116</v>
       </c>
       <c r="C10">
         <v>471.28397822006644</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>1.6400520339478233</v>
+        <v>1.9145940945635918</v>
       </c>
       <c r="B11">
-        <v>19.45307271748743</v>
+        <v>19.205939570342245</v>
       </c>
       <c r="C11">
         <v>471.28397822006644</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>0.10695038144280765</v>
+        <v>0.38647996845446625</v>
       </c>
       <c r="B12">
-        <v>18.238073979508489</v>
+        <v>17.986451235789577</v>
       </c>
       <c r="C12">
         <v>471.28397822006644</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-1.3884004158128041</v>
+        <v>-1.105888149176653</v>
       </c>
       <c r="B13">
-        <v>16.989093243855738</v>
+        <v>16.73478559640705</v>
       </c>
       <c r="C13">
         <v>471.28397822006644</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.8417913126474788</v>
+        <v>-2.5588429249248352</v>
       </c>
       <c r="B14">
-        <v>15.702341675487363</v>
+        <v>15.44764144711173</v>
       </c>
       <c r="C14">
         <v>471.28397822006644</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-4.2708482401969414</v>
+        <v>-3.9878199170558739</v>
       </c>
       <c r="B15">
-        <v>14.393685520264414</v>
+        <v>14.138913336824853</v>
       </c>
       <c r="C15">
         <v>471.28397822006644</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-5.6917370887960557</v>
+        <v>-5.4069760162259248</v>
       </c>
       <c r="B16">
-        <v>13.0776767464569</v>
+        <v>12.821344802670751</v>
       </c>
       <c r="C16">
         <v>471.28397822006644</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-7.092948609269083</v>
+        <v>-6.80625055098194</v>
       </c>
       <c r="B17">
-        <v>11.743955131067658</v>
+        <v>11.485879580581875</v>
       </c>
       <c r="C17">
         <v>471.28397822006644</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-8.4595878587431326</v>
+        <v>-8.1726189425419182</v>
       </c>
       <c r="B18">
-        <v>10.379112768217089</v>
+        <v>10.120793400923848</v>
       </c>
       <c r="C18">
         <v>471.28397822006644</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-9.790892259067304</v>
+        <v>-9.5054185449172266</v>
       </c>
       <c r="B19">
-        <v>8.98246321176303</v>
+        <v>8.7254897729868457</v>
       </c>
       <c r="C19">
         <v>471.28397822006644</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-11.089632323271209</v>
+        <v>-10.80707719531757</v>
       </c>
       <c r="B20">
-        <v>7.5565003804976447</v>
+        <v>7.3021541507921688</v>
       </c>
       <c r="C20">
         <v>471.28397822006644</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-12.358578564384448</v>
+        <v>-12.08002273095266</v>
       </c>
       <c r="B21">
-        <v>6.1037181932131253</v>
+        <v>5.8529719883611415</v>
       </c>
       <c r="C21">
         <v>471.28397822006644</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-13.600004167995049</v>
+        <v>-13.326246638676658</v>
       </c>
       <c r="B22">
-        <v>4.626162891957593</v>
+        <v>4.3797359524081418</v>
       </c>
       <c r="C22">
         <v>471.28397822006644</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-14.814193009924694</v>
+        <v>-14.545995003921496</v>
       </c>
       <c r="B23">
-        <v>3.1240900118030086</v>
+        <v>2.8826675604198853</v>
       </c>
       <c r="C23">
         <v>471.28397822006644</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-16.000931638553496</v>
+        <v>-15.739077561763567</v>
       </c>
       <c r="B24">
-        <v>1.5973074110772625</v>
+        <v>1.3615955425761379</v>
       </c>
       <c r="C24">
         <v>471.28397822006644</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-17.16000660226155</v>
+        <v>-16.905304047279252</v>
       </c>
       <c r="B25">
-        <v>0.045622948108260675</v>
+        <v>-0.18365137094330727</v>
       </c>
       <c r="C25">
         <v>471.28397822006644</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-18.291114942449248</v>
+        <v>-18.04440470508057</v>
       </c>
       <c r="B26">
-        <v>-1.5312360898242419</v>
+        <v>-1.7533160044905325</v>
       </c>
       <c r="C26">
         <v>471.28397822006644</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-19.39359567259811</v>
+        <v>-19.155791817922083</v>
       </c>
       <c r="B27">
-        <v>-3.1338646996332002</v>
+        <v>-3.347927400545148</v>
       </c>
       <c r="C27">
         <v>471.28397822006644</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-20.46669829920992</v>
+        <v>-20.238798178093973</v>
       </c>
       <c r="B28">
-        <v>-4.7629384492796909</v>
+        <v>-4.9680861561185994</v>
       </c>
       <c r="C28">
         <v>471.28397822006644</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-21.509672328786468</v>
+        <v>-21.292756577886415</v>
       </c>
       <c r="B29">
-        <v>-6.4191329067248</v>
+        <v>-6.6143928682223425</v>
       </c>
       <c r="C29">
         <v>471.28397822006644</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-22.522121112555389</v>
+        <v>-22.317308158916806</v>
       </c>
       <c r="B30">
-        <v>-8.1028051213008254</v>
+        <v>-8.2871705686034289</v>
       </c>
       <c r="C30">
         <v>471.28397822006644</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-23.505063380647638</v>
+        <v>-23.313327460111257</v>
       </c>
       <c r="B31">
-        <v>-9.8130380678248361</v>
+        <v>-9.9856320279512278</v>
       </c>
       <c r="C31">
         <v>471.28397822006644</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-24.459871707920023</v>
+        <v>-24.281997369723104</v>
       </c>
       <c r="B32">
-        <v>-11.548596202485099</v>
+        <v>-11.708712451690694</v>
       </c>
       <c r="C32">
         <v>471.28397822006644</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-25.387918669229343</v>
+        <v>-25.224500776005669</v>
       </c>
       <c r="B33">
-        <v>-13.308243981469897</v>
+        <v>-13.455347045246793</v>
       </c>
       <c r="C33">
         <v>471.28397822006644</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-26.28997761669207</v>
+        <v>-26.141494757093646</v>
       </c>
       <c r="B34">
-        <v>-15.091285260290578</v>
+        <v>-15.224944329896788</v>
       </c>
       <c r="C34">
         <v>471.28397822006644</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-27.164425011463404</v>
+        <v>-27.031533150647206</v>
       </c>
       <c r="B35">
-        <v>-16.899181491750895</v>
+        <v>-17.018806090327253</v>
       </c>
       <c r="C35">
         <v>471.28397822006644</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-28.009038091958192</v>
+        <v>-27.892643984207876</v>
       </c>
       <c r="B36">
-        <v>-18.733933527977662</v>
+        <v>-18.838707427077036</v>
       </c>
       <c r="C36">
         <v>471.28397822006644</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-28.821594096591316</v>
+        <v>-28.72285528531722</v>
       </c>
       <c r="B37">
-        <v>-20.597542221097736</v>
+        <v>-20.68642344068504</v>
       </c>
       <c r="C37">
         <v>471.28397822006644</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-29.598417087420657</v>
+        <v>-29.51892200529624</v>
       </c>
       <c r="B38">
-        <v>-22.493316521697054</v>
+        <v>-22.564875210314412</v>
       </c>
       <c r="C38">
         <v>471.28397822006644</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-30.330018421076236</v>
+        <v>-30.272506790583837</v>
       </c>
       <c r="B39">
-        <v>-24.429797774198043</v>
+        <v>-24.481567729625493</v>
       </c>
       <c r="C39">
         <v>471.28397822006644</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-31.005456277831108</v>
+        <v>-30.9739992113984</v>
       </c>
       <c r="B40">
-        <v>-26.416835421482251</v>
+        <v>-26.445151970902884</v>
       </c>
       <c r="C40">
         <v>471.28397822006644</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-30.502143214907814</v>
+        <v>-30.533600281340522</v>
       </c>
       <c r="B43">
-        <v>-26.869900212212432</v>
+        <v>-26.841583662791791</v>
       </c>
       <c r="C43">
         <v>471.28397822006644</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-29.409832333197826</v>
+        <v>-29.467343963690229</v>
       </c>
       <c r="B44">
-        <v>-25.258117061037204</v>
+        <v>-25.206347105609758</v>
       </c>
       <c r="C44">
         <v>471.28397822006644</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-28.326495773429965</v>
+        <v>-28.405990855554382</v>
       </c>
       <c r="B45">
-        <v>-23.638255539574821</v>
+        <v>-23.566696850957463</v>
       </c>
       <c r="C45">
         <v>471.28397822006644</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-27.241773116205845</v>
+        <v>-27.340511927479938</v>
       </c>
       <c r="B46">
-        <v>-22.019641734494584</v>
+        <v>-21.930760514907281</v>
       </c>
       <c r="C46">
         <v>471.28397822006644</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-26.1467323679532</v>
+        <v>-26.263126475703508</v>
       </c>
       <c r="B47">
-        <v>-20.410315913567622</v>
+        <v>-20.305542014468248</v>
       </c>
       <c r="C47">
         <v>471.28397822006644</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-25.038155238404237</v>
+        <v>-25.171047099220431</v>
       </c>
       <c r="B48">
-        <v>-18.813175068972591</v>
+        <v>-18.693550470396236</v>
       </c>
       <c r="C48">
         <v>471.28397822006644</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-23.914251863117261</v>
+        <v>-24.062734722715689</v>
       </c>
       <c r="B49">
-        <v>-17.229830373989948</v>
+        <v>-17.096171304383741</v>
       </c>
       <c r="C49">
         <v>471.28397822006644</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-22.773232377650608</v>
+        <v>-22.936650270874278</v>
       </c>
       <c r="B50">
-        <v>-15.661893001900216</v>
+        <v>-15.51478993812332</v>
       </c>
       <c r="C50">
         <v>471.28397822006644</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-21.613882296769333</v>
+        <v>-21.791756634966248</v>
       </c>
       <c r="B51">
-        <v>-14.110456189774578</v>
+        <v>-13.950339940568988</v>
       </c>
       <c r="C51">
         <v>471.28397822006644</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-20.437288652065533</v>
+        <v>-20.629024572601914</v>
       </c>
       <c r="B52">
-        <v>-12.574541429847084</v>
+        <v>-12.401947469720696</v>
       </c>
       <c r="C52">
         <v>471.28397822006644</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-19.245113854338026</v>
+        <v>-19.44992680797661</v>
       </c>
       <c r="B53">
-        <v>-11.052652278142466</v>
+        <v>-10.868286830839864</v>
       </c>
       <c r="C53">
         <v>471.28397822006644</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-18.039020314385638</v>
+        <v>-18.255936065285692</v>
       </c>
       <c r="B54">
-        <v>-9.5432922906854678</v>
+        <v>-9.3480323291879266</v>
       </c>
       <c r="C54">
         <v>471.28397822006644</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-16.820296361354732</v>
+        <v>-17.048196482470679</v>
       </c>
       <c r="B55">
-        <v>-8.0453017587022142</v>
+        <v>-7.8401540518633075</v>
       </c>
       <c r="C55">
         <v>471.28397822006644</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-15.588733997781684</v>
+        <v>-15.82653785245771</v>
       </c>
       <c r="B56">
-        <v>-6.5588679142243365</v>
+        <v>-6.3448052133123918</v>
       </c>
       <c r="C56">
         <v>471.28397822006644</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-14.343751144550401</v>
+        <v>-14.590461381919079</v>
       </c>
       <c r="B57">
-        <v>-5.0845147244848619</v>
+        <v>-4.8624348098185735</v>
       </c>
       <c r="C57">
         <v>471.28397822006644</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-13.0847657225448</v>
+        <v>-13.339468277527097</v>
       </c>
       <c r="B58">
-        <v>-3.6227661567168177</v>
+        <v>-3.3934918376652514</v>
       </c>
       <c r="C58">
         <v>471.28397822006644</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-11.811266409914685</v>
+        <v>-12.07312048670461</v>
       </c>
       <c r="B59">
-        <v>-2.1740824849406941</v>
+        <v>-1.9383706164395722</v>
       </c>
       <c r="C59">
         <v>471.28397822006644</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-10.523024913873549</v>
+        <v>-10.791222919876745</v>
       </c>
       <c r="B60">
-        <v>-0.7386692103269763</v>
+        <v>-0.4972467589438529</v>
       </c>
       <c r="C60">
         <v>471.28397822006644</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-9.2198836989008068</v>
+        <v>-9.4936412282191966</v>
       </c>
       <c r="B61">
-        <v>0.6833318591663653</v>
+        <v>0.9297587987158159</v>
       </c>
       <c r="C61">
         <v>471.28397822006644</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-7.9016852294758522</v>
+        <v>-8.1802410629076387</v>
       </c>
       <c r="B62">
-        <v>2.091778915581374</v>
+        <v>2.3425251204333581</v>
       </c>
       <c r="C62">
         <v>471.28397822006644</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-6.5687502760129863</v>
+        <v>-6.8513054039666264</v>
       </c>
       <c r="B63">
-        <v>3.48696070521002</v>
+        <v>3.7413069349154968</v>
       </c>
       <c r="C63">
         <v>471.28397822006644</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-5.22331283266604</v>
+        <v>-5.5087865468161183</v>
       </c>
       <c r="B64">
-        <v>4.87088819134407</v>
+        <v>5.1278616301202549</v>
       </c>
       <c r="C64">
         <v>471.28397822006644</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-3.8680851995237426</v>
+        <v>-4.1550541157249539</v>
       </c>
       <c r="B65">
-        <v>6.2460028915252161</v>
+        <v>6.5043222588184566</v>
       </c>
       <c r="C65">
         <v>471.28397822006644</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.5057796766748104</v>
+        <v>-2.7924777349619521</v>
       </c>
       <c r="B66">
-        <v>7.6147463232951651</v>
+        <v>7.8728218737809454</v>
       </c>
       <c r="C66">
         <v>471.28397822006644</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.1355599276739614</v>
+        <v>-1.4203210002440916</v>
       </c>
       <c r="B67">
-        <v>8.976365645878511</v>
+        <v>9.2326975896646584</v>
       </c>
       <c r="C67">
         <v>471.28397822006644</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>0.25760493006012508</v>
+        <v>-0.025423393080939438</v>
       </c>
       <c r="B68">
-        <v>10.317330585231415</v>
+        <v>10.572102768670975</v>
       </c>
       <c r="C68">
         <v>471.28397822006644</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1.6853828909148132</v>
+        <v>1.4024345031921712</v>
       </c>
       <c r="B69">
-        <v>11.627138021477256</v>
+        <v>11.881838249852887</v>
       </c>
       <c r="C69">
         <v>471.28397822006644</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>3.1317958503655947</v>
+        <v>2.8492835837294441</v>
       </c>
       <c r="B70">
-        <v>12.920170884676727</v>
+        <v>13.174478532125415</v>
       </c>
       <c r="C70">
         <v>471.28397822006644</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>4.57942377362932</v>
+        <v>4.2998941866176645</v>
       </c>
       <c r="B71">
-        <v>14.212110080005839</v>
+        <v>14.463732823724754</v>
       </c>
       <c r="C71">
         <v>471.28397822006644</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6.0327250038001</v>
+        <v>5.758182943184333</v>
       </c>
       <c r="B72">
-        <v>15.498942363164494</v>
+        <v>15.746075510309675</v>
       </c>
       <c r="C72">
         <v>471.28397822006644</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>7.4990766364498063</v>
+        <v>7.2306217368470209</v>
       </c>
       <c r="B73">
-        <v>16.774027131101267</v>
+        <v>17.015680829105058</v>
       </c>
       <c r="C73">
         <v>471.28397822006644</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>8.9756523991840957</v>
+        <v>8.7147571661427978</v>
       </c>
       <c r="B74">
-        <v>18.039908495235512</v>
+        <v>18.274757246177575</v>
       </c>
       <c r="C74">
         <v>471.28397822006644</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>10.457024886487517</v>
+        <v>10.205861221254873</v>
       </c>
       <c r="B75">
-        <v>19.30147201591766</v>
+        <v>19.527560750366018</v>
       </c>
       <c r="C75">
         <v>471.28397822006644</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>11.937565528326369</v>
+        <v>11.699032743831467</v>
       </c>
       <c r="B76">
-        <v>20.563784334751659</v>
+        <v>20.778503192755828</v>
       </c>
       <c r="C76">
         <v>471.28397822006644</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>13.41208867467596</v>
+        <v>13.18975966082923</v>
       </c>
       <c r="B77">
-        <v>21.831513392262636</v>
+        <v>22.031646183465529</v>
       </c>
       <c r="C77">
         <v>471.28397822006644</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>14.877381520065804</v>
+        <v>14.675259388973368</v>
       </c>
       <c r="B78">
-        <v>23.107551243406771</v>
+        <v>23.289494506499246</v>
       </c>
       <c r="C78">
         <v>471.28397822006644</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>16.327823281360025</v>
+        <v>16.150643881338571</v>
       </c>
       <c r="B79">
-        <v>24.396957520295356</v>
+        <v>24.556448210495567</v>
       </c>
       <c r="C79">
         <v>471.28397822006644</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>17.753401788115024</v>
+        <v>17.60718577838858</v>
       </c>
       <c r="B80">
-        <v>25.708744828085972</v>
+        <v>25.84036335883372</v>
       </c>
       <c r="C80">
         <v>471.28397822006644</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>19.12917445744025</v>
+        <v>19.023096175874009</v>
       </c>
       <c r="B81">
-        <v>27.065365606284058</v>
+        <v>27.160853559963797</v>
       </c>
       <c r="C81">
         <v>471.28397822006644</v>
